--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-dicom-informations-cliniques.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-dicom-informations-cliniques.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2731" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2749" uniqueCount="292">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -489,6 +489,9 @@
 </t>
   </si>
   <si>
+    <t>Can serve as a target of a linkHtml reference</t>
+  </si>
+  <si>
     <t>Section.classCode</t>
   </si>
   <si>
@@ -678,6 +681,9 @@
     <t>Titre de la section</t>
   </si>
   <si>
+    <t>If valued, it is to be rendered as part of the narrative content of the clinical document body.</t>
+  </si>
+  <si>
     <t>Section.text</t>
   </si>
   <si>
@@ -688,10 +694,25 @@
     <t>Bloc narratif</t>
   </si>
   <si>
+    <t>Also referred to as the CDA Narrative Block</t>
+  </si>
+  <si>
     <t>Section.confidentialityCode</t>
   </si>
   <si>
+    <t>Controls the disclosure of information in this section</t>
+  </si>
+  <si>
+    <t>A value for Section.confidentialityCode overrides the value propagated from StructuredBody.</t>
+  </si>
+  <si>
     <t>Section.languageCode</t>
+  </si>
+  <si>
+    <t>Human language of character data</t>
+  </si>
+  <si>
+    <t>A value for Section.languageCode overrides the value propagated from StructuredBody.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/all-languages</t>
@@ -704,6 +725,15 @@
 </t>
   </si>
   <si>
+    <t>Primary target of the entries recorded in a section</t>
+  </si>
+  <si>
+    <t>Most of the time the subject is the same as the recordTarget, but need not be, for instance when the subject is a fetus observed in an obstetrical ultrasound.</t>
+  </si>
+  <si>
+    <t>The subject participant can be ascribed to a CDA section or a CDA entry. It propagates to nested components, unless overridden. The subject of a document is presumed to be the patient.</t>
+  </si>
+  <si>
     <t>Section.author</t>
   </si>
   <si>
@@ -711,6 +741,9 @@
 </t>
   </si>
   <si>
+    <t>The author participant can be ascribed to a CDA section, where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.informant</t>
   </si>
   <si>
@@ -718,6 +751,9 @@
 </t>
   </si>
   <si>
+    <t>The informant participant can be ascribed to a CDA section where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.entry</t>
   </si>
   <si>
@@ -730,6 +766,12 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
 </t>
+  </si>
+  <si>
+    <t>Used to nest a Section within a Section</t>
+  </si>
+  <si>
+    <t>Context propagates to nested sections</t>
   </si>
   <si>
     <t xml:space="preserve">type:$this}
@@ -1214,7 +1256,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="148.87109375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -3635,7 +3677,9 @@
       <c r="K24" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L24" s="2"/>
+      <c r="L24" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3706,10 +3750,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3743,7 +3787,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>74</v>
@@ -3765,7 +3809,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>74</v>
@@ -3783,7 +3827,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3803,10 +3847,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3840,7 +3884,7 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>74</v>
@@ -3862,7 +3906,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>74</v>
@@ -3880,7 +3924,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3900,10 +3944,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3917,7 +3961,7 @@
         <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>74</v>
@@ -3929,10 +3973,10 @@
         <v>95</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3983,7 +4027,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4003,10 +4047,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4020,7 +4064,7 @@
         <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>74</v>
@@ -4029,13 +4073,13 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4086,7 +4130,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4106,10 +4150,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4207,10 +4251,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4239,7 +4283,7 @@
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4251,7 +4295,7 @@
         <v>74</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>74</v>
@@ -4290,7 +4334,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4310,17 +4354,17 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>75</v>
@@ -4342,7 +4386,7 @@
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4354,7 +4398,7 @@
         <v>74</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>74</v>
@@ -4393,7 +4437,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4413,17 +4457,17 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4445,7 +4489,7 @@
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4457,7 +4501,7 @@
         <v>74</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>74</v>
@@ -4496,7 +4540,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4516,17 +4560,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -4548,7 +4592,7 @@
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4599,7 +4643,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4619,17 +4663,17 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>75</v>
@@ -4651,7 +4695,7 @@
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4663,7 +4707,7 @@
         <v>74</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>74</v>
@@ -4702,7 +4746,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4722,10 +4766,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4748,11 +4792,11 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4803,7 +4847,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4823,10 +4867,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4853,7 +4897,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4904,7 +4948,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4924,17 +4968,17 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
@@ -4952,11 +4996,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5007,7 +5051,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5027,17 +5071,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -5055,11 +5099,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5110,7 +5154,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5130,17 +5174,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5158,11 +5202,11 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5213,7 +5257,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5233,10 +5277,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5250,7 +5294,7 @@
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5259,16 +5303,18 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>74</v>
       </c>
@@ -5316,7 +5362,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5336,10 +5382,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5353,7 +5399,7 @@
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -5362,15 +5408,17 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>74</v>
@@ -5419,7 +5467,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5439,10 +5487,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5465,12 +5513,16 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="L42" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>74</v>
       </c>
@@ -5518,7 +5570,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5538,10 +5590,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5566,10 +5618,14 @@
       <c r="K43" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L43" s="2"/>
+      <c r="L43" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>74</v>
       </c>
@@ -5597,7 +5653,7 @@
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>74</v>
@@ -5615,7 +5671,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5635,10 +5691,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5661,12 +5717,18 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="L44" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="M44" s="2"/>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="N44" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>74</v>
       </c>
@@ -5714,7 +5776,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5734,10 +5796,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5760,12 +5822,14 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>74</v>
       </c>
@@ -5813,7 +5877,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5833,10 +5897,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5859,12 +5923,14 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>74</v>
       </c>
@@ -5912,7 +5978,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -5932,10 +5998,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5958,7 +6024,7 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -6011,7 +6077,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6031,10 +6097,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6048,7 +6114,7 @@
         <v>121</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>74</v>
@@ -6057,12 +6123,16 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="L48" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>74</v>
       </c>
@@ -6098,7 +6168,7 @@
         <v>74</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="AC48" s="2"/>
       <c r="AD48" t="s" s="2">
@@ -6108,7 +6178,7 @@
         <v>124</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6128,10 +6198,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6229,10 +6299,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6330,10 +6400,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6431,10 +6501,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6532,10 +6602,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6635,10 +6705,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6738,10 +6808,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6841,10 +6911,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6944,10 +7014,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7045,10 +7115,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7075,7 +7145,7 @@
       </c>
       <c r="L58" s="2"/>
       <c r="M58" t="s" s="2">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7084,7 +7154,7 @@
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>74</v>
@@ -7126,7 +7196,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7146,10 +7216,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7183,7 +7253,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>74</v>
@@ -7225,7 +7295,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7245,10 +7315,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7271,7 +7341,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7324,7 +7394,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>
@@ -7344,13 +7414,13 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>74</v>
@@ -7372,12 +7442,16 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="L61" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+      <c r="O61" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>74</v>
       </c>
@@ -7425,7 +7499,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7445,10 +7519,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7546,10 +7620,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7647,10 +7721,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7748,10 +7822,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7849,10 +7923,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -7952,10 +8026,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8055,10 +8129,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8158,10 +8232,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8261,10 +8335,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8362,10 +8436,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8392,7 +8466,7 @@
       </c>
       <c r="L71" s="2"/>
       <c r="M71" t="s" s="2">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8401,7 +8475,7 @@
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>74</v>
@@ -8443,7 +8517,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8463,10 +8537,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8500,7 +8574,7 @@
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>74</v>
@@ -8542,7 +8616,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8562,10 +8636,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8588,10 +8662,10 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
@@ -8643,7 +8717,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>75</v>
@@ -8663,13 +8737,13 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>74</v>
@@ -8691,12 +8765,16 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="L74" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>74</v>
       </c>
@@ -8744,7 +8822,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8764,10 +8842,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8865,10 +8943,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -8966,10 +9044,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9067,10 +9145,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9168,10 +9246,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9271,10 +9349,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9374,10 +9452,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9477,10 +9555,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9580,10 +9658,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9681,10 +9759,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9711,7 +9789,7 @@
       </c>
       <c r="L84" s="2"/>
       <c r="M84" t="s" s="2">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -9720,7 +9798,7 @@
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>74</v>
@@ -9762,7 +9840,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -9782,10 +9860,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9819,7 +9897,7 @@
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>74</v>
@@ -9861,7 +9939,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -9881,10 +9959,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -9907,10 +9985,10 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
@@ -9962,7 +10040,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>75</v>
